--- a/docs/06-原型效果图/后台管理/模板文件/知识体系设计/法规库批量导入模板.xlsx
+++ b/docs/06-原型效果图/后台管理/模板文件/知识体系设计/法规库批量导入模板.xlsx
@@ -9,7 +9,16 @@
   <sheets>
     <sheet name="导入模板" sheetId="1" r:id="rId1"/>
     <sheet name="填写说明" sheetId="2" r:id="rId2"/>
+    <sheet name="区域数据" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="省">区域数据!$A$1:$C$1</definedName>
+    <definedName name="P_全国">区域数据!$B$3:$B$3</definedName>
+    <definedName name="P_广东省">区域数据!$B$4:$B$4</definedName>
+    <definedName name="P_上海市">区域数据!$B$5:$B$5</definedName>
+    <definedName name="C_深圳市">区域数据!$B$7:$J$7</definedName>
+    <definedName name="C_上海市">区域数据!$B$8:$Q$8</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -28,11 +37,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="73">
   <si>
     <t>适用行业</t>
   </si>
   <si>
+    <t>省</t>
+  </si>
+  <si>
+    <t>市</t>
+  </si>
+  <si>
+    <t>区县</t>
+  </si>
+  <si>
     <t>法规编号</t>
   </si>
   <si>
@@ -54,6 +72,12 @@
     <t>建筑施工</t>
   </si>
   <si>
+    <t>上海市</t>
+  </si>
+  <si>
+    <t>青浦区</t>
+  </si>
+  <si>
     <t>JGJ80-2016</t>
   </si>
   <si>
@@ -93,6 +117,27 @@
     <t>页面展示中文行业名称，系统内部映射行业域代码。</t>
   </si>
   <si>
+    <t>全国 / 广东省 / 上海市</t>
+  </si>
+  <si>
+    <t>适用地区至少选择到省级；全国适用请选择全国，市和区县留空。</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>深圳市 / 上海市</t>
+  </si>
+  <si>
+    <t>选择省级地区后按省联动选择；选择全国时留空。</t>
+  </si>
+  <si>
+    <t>南山区 / 黄浦区</t>
+  </si>
+  <si>
+    <t>可选择到区县，也可停留在全国、省、市层级；不支持街镇/社区。</t>
+  </si>
+  <si>
     <t>官方编号。</t>
   </si>
   <si>
@@ -111,25 +156,106 @@
     <t>可选：国家标准 / 行业标准 / 地方标准 / 企业标准。</t>
   </si>
   <si>
-    <t>否</t>
-  </si>
-  <si>
     <t>特殊情况说明</t>
   </si>
   <si>
     <t>补充信息。</t>
   </si>
   <si>
-    <t>条款编码</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>系统自动生成</t>
-  </si>
-  <si>
-    <t>系统自动生成，不需要在Excel中填写。</t>
+    <t>导入展示</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>广东省 / 深圳市 / 南山区</t>
+  </si>
+  <si>
+    <t>系统导入后将省、市、区县合并为一个适用地区字段展示。</t>
+  </si>
+  <si>
+    <t>全国</t>
+  </si>
+  <si>
+    <t>广东省</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>深圳市</t>
+  </si>
+  <si>
+    <t>罗湖区</t>
+  </si>
+  <si>
+    <t>福田区</t>
+  </si>
+  <si>
+    <t>南山区</t>
+  </si>
+  <si>
+    <t>宝安区</t>
+  </si>
+  <si>
+    <t>龙岗区</t>
+  </si>
+  <si>
+    <t>盐田区</t>
+  </si>
+  <si>
+    <t>龙华区</t>
+  </si>
+  <si>
+    <t>坪山区</t>
+  </si>
+  <si>
+    <t>光明区</t>
+  </si>
+  <si>
+    <t>黄浦区</t>
+  </si>
+  <si>
+    <t>徐汇区</t>
+  </si>
+  <si>
+    <t>长宁区</t>
+  </si>
+  <si>
+    <t>静安区</t>
+  </si>
+  <si>
+    <t>普陀区</t>
+  </si>
+  <si>
+    <t>虹口区</t>
+  </si>
+  <si>
+    <t>杨浦区</t>
+  </si>
+  <si>
+    <t>闵行区</t>
+  </si>
+  <si>
+    <t>宝山区</t>
+  </si>
+  <si>
+    <t>嘉定区</t>
+  </si>
+  <si>
+    <t>浦东新区</t>
+  </si>
+  <si>
+    <t>金山区</t>
+  </si>
+  <si>
+    <t>松江区</t>
+  </si>
+  <si>
+    <t>奉贤区</t>
+  </si>
+  <si>
+    <t>崇明区</t>
   </si>
 </sst>
 </file>
@@ -142,7 +268,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,13 +287,6 @@
       <sz val="10"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -650,160 +769,157 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1161,66 +1277,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G200"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="25" customHeight="1" outlineLevelCol="6"/>
+  <dimension ref="A1:J200"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16" style="4" customWidth="1"/>
-    <col min="2" max="2" width="18" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30" style="4" customWidth="1"/>
-    <col min="4" max="4" width="16" style="4" customWidth="1"/>
-    <col min="5" max="5" width="46" style="4" customWidth="1"/>
-    <col min="6" max="6" width="16" style="4" customWidth="1"/>
-    <col min="7" max="7" width="24" style="4" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="16" style="3" customWidth="1"/>
+    <col min="2" max="4" width="14" style="3" customWidth="1"/>
+    <col min="5" max="5" width="18" style="3" customWidth="1"/>
+    <col min="6" max="6" width="30" style="3" customWidth="1"/>
+    <col min="7" max="7" width="16" style="3" customWidth="1"/>
+    <col min="8" max="8" width="46" style="3" customWidth="1"/>
+    <col min="9" max="9" width="16" style="3" customWidth="1"/>
+    <col min="10" max="10" width="24" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="46" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:7">
-      <c r="A1" s="5" t="s">
+    <row r="1" customHeight="1" spans="1:10">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:7">
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:7">
+        <v>15</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:10">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1228,8 +1363,11 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-    </row>
-    <row r="4" customHeight="1" spans="1:7">
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:10">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1237,8 +1375,11 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-    </row>
-    <row r="5" customHeight="1" spans="1:7">
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:10">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1246,8 +1387,11 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:7">
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:10">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1255,8 +1399,11 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:7">
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:10">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1264,8 +1411,11 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:7">
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:10">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1273,8 +1423,11 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:7">
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:10">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1282,8 +1435,11 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:7">
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:10">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1291,8 +1447,11 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:7">
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:10">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1300,8 +1459,11 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:7">
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:10">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1309,8 +1471,11 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:7">
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:10">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1318,8 +1483,11 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:7">
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:10">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1327,8 +1495,11 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:7">
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:10">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1336,8 +1507,11 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:7">
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:10">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1345,8 +1519,11 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:7">
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:10">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -1354,8 +1531,11 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:7">
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:10">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1363,8 +1543,11 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:7">
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:10">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1372,8 +1555,11 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:7">
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:10">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1381,8 +1567,11 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:7">
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:10">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -1390,8 +1579,11 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:7">
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:10">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1399,8 +1591,11 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:7">
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:10">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1408,8 +1603,11 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:7">
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:10">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1417,8 +1615,11 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:7">
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:10">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -1426,8 +1627,11 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:7">
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:10">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1435,8 +1639,11 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:7">
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:10">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1444,8 +1651,11 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:7">
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:10">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -1453,8 +1663,11 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:7">
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:10">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -1462,8 +1675,11 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:7">
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:10">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1471,8 +1687,11 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:7">
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:10">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -1480,8 +1699,11 @@
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:7">
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:10">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -1489,8 +1711,11 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:7">
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:10">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -1498,8 +1723,11 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:7">
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:10">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -1507,8 +1735,11 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
-    </row>
-    <row r="35" customHeight="1" spans="1:7">
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:10">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -1516,8 +1747,11 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:7">
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:10">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -1525,8 +1759,11 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:7">
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:10">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -1534,8 +1771,11 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:7">
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:10">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -1543,8 +1783,11 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:7">
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:10">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -1552,8 +1795,11 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:7">
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:10">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -1561,8 +1807,11 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:7">
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:10">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -1570,8 +1819,11 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:7">
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:10">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -1579,8 +1831,11 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:7">
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:10">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -1588,8 +1843,11 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:7">
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:10">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -1597,8 +1855,11 @@
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:7">
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:10">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -1606,8 +1867,11 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:7">
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:10">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -1615,8 +1879,11 @@
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:7">
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:10">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -1624,8 +1891,11 @@
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:7">
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:10">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -1633,8 +1903,11 @@
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-    </row>
-    <row r="49" customHeight="1" spans="1:7">
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:10">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -1642,8 +1915,11 @@
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-    </row>
-    <row r="50" customHeight="1" spans="1:7">
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:10">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -1651,8 +1927,11 @@
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-    </row>
-    <row r="51" customHeight="1" spans="1:7">
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:10">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -1660,8 +1939,11 @@
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-    </row>
-    <row r="52" customHeight="1" spans="1:7">
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:10">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -1669,8 +1951,11 @@
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-    </row>
-    <row r="53" customHeight="1" spans="1:7">
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+    </row>
+    <row r="53" customHeight="1" spans="1:10">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -1678,8 +1963,11 @@
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-    </row>
-    <row r="54" customHeight="1" spans="1:7">
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+    </row>
+    <row r="54" customHeight="1" spans="1:10">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -1687,8 +1975,11 @@
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-    </row>
-    <row r="55" customHeight="1" spans="1:7">
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+    </row>
+    <row r="55" customHeight="1" spans="1:10">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -1696,8 +1987,11 @@
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
-    </row>
-    <row r="56" customHeight="1" spans="1:7">
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+    </row>
+    <row r="56" customHeight="1" spans="1:10">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -1705,8 +1999,11 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-    </row>
-    <row r="57" customHeight="1" spans="1:7">
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+    </row>
+    <row r="57" customHeight="1" spans="1:10">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -1714,8 +2011,11 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-    </row>
-    <row r="58" customHeight="1" spans="1:7">
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+    </row>
+    <row r="58" customHeight="1" spans="1:10">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -1723,8 +2023,11 @@
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-    </row>
-    <row r="59" customHeight="1" spans="1:7">
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+    </row>
+    <row r="59" customHeight="1" spans="1:10">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -1732,8 +2035,11 @@
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
-    </row>
-    <row r="60" customHeight="1" spans="1:7">
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+    </row>
+    <row r="60" customHeight="1" spans="1:10">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -1741,8 +2047,11 @@
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-    </row>
-    <row r="61" customHeight="1" spans="1:7">
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+    </row>
+    <row r="61" customHeight="1" spans="1:10">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -1750,8 +2059,11 @@
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
-    </row>
-    <row r="62" customHeight="1" spans="1:7">
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+    </row>
+    <row r="62" customHeight="1" spans="1:10">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -1759,8 +2071,11 @@
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-    </row>
-    <row r="63" customHeight="1" spans="1:7">
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+    </row>
+    <row r="63" customHeight="1" spans="1:10">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -1768,8 +2083,11 @@
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
-    </row>
-    <row r="64" customHeight="1" spans="1:7">
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+    </row>
+    <row r="64" customHeight="1" spans="1:10">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -1777,8 +2095,11 @@
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
-    </row>
-    <row r="65" customHeight="1" spans="1:7">
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+    </row>
+    <row r="65" customHeight="1" spans="1:10">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -1786,8 +2107,11 @@
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-    </row>
-    <row r="66" customHeight="1" spans="1:7">
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+    </row>
+    <row r="66" customHeight="1" spans="1:10">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -1795,8 +2119,11 @@
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-    </row>
-    <row r="67" customHeight="1" spans="1:7">
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+    </row>
+    <row r="67" customHeight="1" spans="1:10">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -1804,8 +2131,11 @@
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-    </row>
-    <row r="68" customHeight="1" spans="1:7">
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+    </row>
+    <row r="68" customHeight="1" spans="1:10">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -1813,8 +2143,11 @@
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-    </row>
-    <row r="69" customHeight="1" spans="1:7">
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+    </row>
+    <row r="69" customHeight="1" spans="1:10">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -1822,8 +2155,11 @@
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
-    </row>
-    <row r="70" customHeight="1" spans="1:7">
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+    </row>
+    <row r="70" customHeight="1" spans="1:10">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -1831,8 +2167,11 @@
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-    </row>
-    <row r="71" customHeight="1" spans="1:7">
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+    </row>
+    <row r="71" customHeight="1" spans="1:10">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -1840,8 +2179,11 @@
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-    </row>
-    <row r="72" customHeight="1" spans="1:7">
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+    </row>
+    <row r="72" customHeight="1" spans="1:10">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -1849,8 +2191,11 @@
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
-    </row>
-    <row r="73" customHeight="1" spans="1:7">
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+    </row>
+    <row r="73" customHeight="1" spans="1:10">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -1858,8 +2203,11 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
-    </row>
-    <row r="74" customHeight="1" spans="1:7">
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+    </row>
+    <row r="74" customHeight="1" spans="1:10">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -1867,8 +2215,11 @@
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
-    </row>
-    <row r="75" customHeight="1" spans="1:7">
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+    </row>
+    <row r="75" customHeight="1" spans="1:10">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -1876,8 +2227,11 @@
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
-    </row>
-    <row r="76" customHeight="1" spans="1:7">
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+    </row>
+    <row r="76" customHeight="1" spans="1:10">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -1885,8 +2239,11 @@
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
-    </row>
-    <row r="77" customHeight="1" spans="1:7">
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+    </row>
+    <row r="77" customHeight="1" spans="1:10">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -1894,8 +2251,11 @@
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
-    </row>
-    <row r="78" customHeight="1" spans="1:7">
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+    </row>
+    <row r="78" customHeight="1" spans="1:10">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -1903,8 +2263,11 @@
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
-    </row>
-    <row r="79" customHeight="1" spans="1:7">
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
+    </row>
+    <row r="79" customHeight="1" spans="1:10">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -1912,8 +2275,11 @@
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
-    </row>
-    <row r="80" customHeight="1" spans="1:7">
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+    </row>
+    <row r="80" customHeight="1" spans="1:10">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -1921,8 +2287,11 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
-    </row>
-    <row r="81" customHeight="1" spans="1:7">
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+      <c r="J80" s="2"/>
+    </row>
+    <row r="81" customHeight="1" spans="1:10">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -1930,8 +2299,11 @@
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
-    </row>
-    <row r="82" customHeight="1" spans="1:7">
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+    </row>
+    <row r="82" customHeight="1" spans="1:10">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -1939,8 +2311,11 @@
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
-    </row>
-    <row r="83" customHeight="1" spans="1:7">
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+      <c r="J82" s="2"/>
+    </row>
+    <row r="83" customHeight="1" spans="1:10">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -1948,8 +2323,11 @@
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
-    </row>
-    <row r="84" customHeight="1" spans="1:7">
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
+    </row>
+    <row r="84" customHeight="1" spans="1:10">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -1957,8 +2335,11 @@
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
-    </row>
-    <row r="85" customHeight="1" spans="1:7">
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
+    </row>
+    <row r="85" customHeight="1" spans="1:10">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -1966,8 +2347,11 @@
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
-    </row>
-    <row r="86" customHeight="1" spans="1:7">
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2"/>
+    </row>
+    <row r="86" customHeight="1" spans="1:10">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -1975,8 +2359,11 @@
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
-    </row>
-    <row r="87" customHeight="1" spans="1:7">
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+      <c r="J86" s="2"/>
+    </row>
+    <row r="87" customHeight="1" spans="1:10">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -1984,8 +2371,11 @@
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
-    </row>
-    <row r="88" customHeight="1" spans="1:7">
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
+    </row>
+    <row r="88" customHeight="1" spans="1:10">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -1993,8 +2383,11 @@
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
-    </row>
-    <row r="89" customHeight="1" spans="1:7">
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+      <c r="J88" s="2"/>
+    </row>
+    <row r="89" customHeight="1" spans="1:10">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -2002,8 +2395,11 @@
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
-    </row>
-    <row r="90" customHeight="1" spans="1:7">
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+    </row>
+    <row r="90" customHeight="1" spans="1:10">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -2011,8 +2407,11 @@
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
-    </row>
-    <row r="91" customHeight="1" spans="1:7">
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
+    </row>
+    <row r="91" customHeight="1" spans="1:10">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -2020,8 +2419,11 @@
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
-    </row>
-    <row r="92" customHeight="1" spans="1:7">
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+    </row>
+    <row r="92" customHeight="1" spans="1:10">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -2029,8 +2431,11 @@
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
-    </row>
-    <row r="93" customHeight="1" spans="1:7">
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+    </row>
+    <row r="93" customHeight="1" spans="1:10">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -2038,8 +2443,11 @@
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
-    </row>
-    <row r="94" customHeight="1" spans="1:7">
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+    </row>
+    <row r="94" customHeight="1" spans="1:10">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -2047,8 +2455,11 @@
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
-    </row>
-    <row r="95" customHeight="1" spans="1:7">
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
+    </row>
+    <row r="95" customHeight="1" spans="1:10">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -2056,8 +2467,11 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
-    </row>
-    <row r="96" customHeight="1" spans="1:7">
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
+    </row>
+    <row r="96" customHeight="1" spans="1:10">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -2065,8 +2479,11 @@
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
-    </row>
-    <row r="97" customHeight="1" spans="1:7">
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
+    </row>
+    <row r="97" customHeight="1" spans="1:10">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -2074,8 +2491,11 @@
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
-    </row>
-    <row r="98" customHeight="1" spans="1:7">
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
+    </row>
+    <row r="98" customHeight="1" spans="1:10">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -2083,8 +2503,11 @@
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
-    </row>
-    <row r="99" customHeight="1" spans="1:7">
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
+    </row>
+    <row r="99" customHeight="1" spans="1:10">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -2092,8 +2515,11 @@
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
-    </row>
-    <row r="100" customHeight="1" spans="1:7">
+      <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="2"/>
+    </row>
+    <row r="100" customHeight="1" spans="1:10">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -2101,8 +2527,11 @@
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
-    </row>
-    <row r="101" customHeight="1" spans="1:7">
+      <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+      <c r="J100" s="2"/>
+    </row>
+    <row r="101" customHeight="1" spans="1:10">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -2110,8 +2539,11 @@
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
-    </row>
-    <row r="102" customHeight="1" spans="1:7">
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="2"/>
+    </row>
+    <row r="102" customHeight="1" spans="1:10">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -2119,8 +2551,11 @@
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
-    </row>
-    <row r="103" customHeight="1" spans="1:7">
+      <c r="H102" s="2"/>
+      <c r="I102" s="2"/>
+      <c r="J102" s="2"/>
+    </row>
+    <row r="103" customHeight="1" spans="1:10">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -2128,8 +2563,11 @@
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
-    </row>
-    <row r="104" customHeight="1" spans="1:7">
+      <c r="H103" s="2"/>
+      <c r="I103" s="2"/>
+      <c r="J103" s="2"/>
+    </row>
+    <row r="104" customHeight="1" spans="1:10">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -2137,8 +2575,11 @@
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
-    </row>
-    <row r="105" customHeight="1" spans="1:7">
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
+      <c r="J104" s="2"/>
+    </row>
+    <row r="105" customHeight="1" spans="1:10">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -2146,8 +2587,11 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
-    </row>
-    <row r="106" customHeight="1" spans="1:7">
+      <c r="H105" s="2"/>
+      <c r="I105" s="2"/>
+      <c r="J105" s="2"/>
+    </row>
+    <row r="106" customHeight="1" spans="1:10">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -2155,8 +2599,11 @@
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
-    </row>
-    <row r="107" customHeight="1" spans="1:7">
+      <c r="H106" s="2"/>
+      <c r="I106" s="2"/>
+      <c r="J106" s="2"/>
+    </row>
+    <row r="107" customHeight="1" spans="1:10">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -2164,8 +2611,11 @@
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
-    </row>
-    <row r="108" customHeight="1" spans="1:7">
+      <c r="H107" s="2"/>
+      <c r="I107" s="2"/>
+      <c r="J107" s="2"/>
+    </row>
+    <row r="108" customHeight="1" spans="1:10">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -2173,8 +2623,11 @@
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
-    </row>
-    <row r="109" customHeight="1" spans="1:7">
+      <c r="H108" s="2"/>
+      <c r="I108" s="2"/>
+      <c r="J108" s="2"/>
+    </row>
+    <row r="109" customHeight="1" spans="1:10">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -2182,8 +2635,11 @@
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
-    </row>
-    <row r="110" customHeight="1" spans="1:7">
+      <c r="H109" s="2"/>
+      <c r="I109" s="2"/>
+      <c r="J109" s="2"/>
+    </row>
+    <row r="110" customHeight="1" spans="1:10">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -2191,8 +2647,11 @@
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
-    </row>
-    <row r="111" customHeight="1" spans="1:7">
+      <c r="H110" s="2"/>
+      <c r="I110" s="2"/>
+      <c r="J110" s="2"/>
+    </row>
+    <row r="111" customHeight="1" spans="1:10">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -2200,8 +2659,11 @@
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
-    </row>
-    <row r="112" customHeight="1" spans="1:7">
+      <c r="H111" s="2"/>
+      <c r="I111" s="2"/>
+      <c r="J111" s="2"/>
+    </row>
+    <row r="112" customHeight="1" spans="1:10">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -2209,8 +2671,11 @@
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
-    </row>
-    <row r="113" customHeight="1" spans="1:7">
+      <c r="H112" s="2"/>
+      <c r="I112" s="2"/>
+      <c r="J112" s="2"/>
+    </row>
+    <row r="113" customHeight="1" spans="1:10">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -2218,8 +2683,11 @@
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
-    </row>
-    <row r="114" customHeight="1" spans="1:7">
+      <c r="H113" s="2"/>
+      <c r="I113" s="2"/>
+      <c r="J113" s="2"/>
+    </row>
+    <row r="114" customHeight="1" spans="1:10">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -2227,8 +2695,11 @@
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
-    </row>
-    <row r="115" customHeight="1" spans="1:7">
+      <c r="H114" s="2"/>
+      <c r="I114" s="2"/>
+      <c r="J114" s="2"/>
+    </row>
+    <row r="115" customHeight="1" spans="1:10">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -2236,8 +2707,11 @@
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
-    </row>
-    <row r="116" customHeight="1" spans="1:7">
+      <c r="H115" s="2"/>
+      <c r="I115" s="2"/>
+      <c r="J115" s="2"/>
+    </row>
+    <row r="116" customHeight="1" spans="1:10">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -2245,8 +2719,11 @@
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
-    </row>
-    <row r="117" customHeight="1" spans="1:7">
+      <c r="H116" s="2"/>
+      <c r="I116" s="2"/>
+      <c r="J116" s="2"/>
+    </row>
+    <row r="117" customHeight="1" spans="1:10">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -2254,8 +2731,11 @@
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
-    </row>
-    <row r="118" customHeight="1" spans="1:7">
+      <c r="H117" s="2"/>
+      <c r="I117" s="2"/>
+      <c r="J117" s="2"/>
+    </row>
+    <row r="118" customHeight="1" spans="1:10">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -2263,8 +2743,11 @@
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
-    </row>
-    <row r="119" customHeight="1" spans="1:7">
+      <c r="H118" s="2"/>
+      <c r="I118" s="2"/>
+      <c r="J118" s="2"/>
+    </row>
+    <row r="119" customHeight="1" spans="1:10">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -2272,8 +2755,11 @@
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
-    </row>
-    <row r="120" customHeight="1" spans="1:7">
+      <c r="H119" s="2"/>
+      <c r="I119" s="2"/>
+      <c r="J119" s="2"/>
+    </row>
+    <row r="120" customHeight="1" spans="1:10">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -2281,8 +2767,11 @@
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
-    </row>
-    <row r="121" customHeight="1" spans="1:7">
+      <c r="H120" s="2"/>
+      <c r="I120" s="2"/>
+      <c r="J120" s="2"/>
+    </row>
+    <row r="121" customHeight="1" spans="1:10">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -2290,8 +2779,11 @@
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
-    </row>
-    <row r="122" customHeight="1" spans="1:7">
+      <c r="H121" s="2"/>
+      <c r="I121" s="2"/>
+      <c r="J121" s="2"/>
+    </row>
+    <row r="122" customHeight="1" spans="1:10">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -2299,8 +2791,11 @@
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
-    </row>
-    <row r="123" customHeight="1" spans="1:7">
+      <c r="H122" s="2"/>
+      <c r="I122" s="2"/>
+      <c r="J122" s="2"/>
+    </row>
+    <row r="123" customHeight="1" spans="1:10">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -2308,8 +2803,11 @@
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
-    </row>
-    <row r="124" customHeight="1" spans="1:7">
+      <c r="H123" s="2"/>
+      <c r="I123" s="2"/>
+      <c r="J123" s="2"/>
+    </row>
+    <row r="124" customHeight="1" spans="1:10">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -2317,8 +2815,11 @@
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
-    </row>
-    <row r="125" customHeight="1" spans="1:7">
+      <c r="H124" s="2"/>
+      <c r="I124" s="2"/>
+      <c r="J124" s="2"/>
+    </row>
+    <row r="125" customHeight="1" spans="1:10">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -2326,8 +2827,11 @@
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
-    </row>
-    <row r="126" customHeight="1" spans="1:7">
+      <c r="H125" s="2"/>
+      <c r="I125" s="2"/>
+      <c r="J125" s="2"/>
+    </row>
+    <row r="126" customHeight="1" spans="1:10">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -2335,8 +2839,11 @@
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
-    </row>
-    <row r="127" customHeight="1" spans="1:7">
+      <c r="H126" s="2"/>
+      <c r="I126" s="2"/>
+      <c r="J126" s="2"/>
+    </row>
+    <row r="127" customHeight="1" spans="1:10">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -2344,8 +2851,11 @@
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
-    </row>
-    <row r="128" customHeight="1" spans="1:7">
+      <c r="H127" s="2"/>
+      <c r="I127" s="2"/>
+      <c r="J127" s="2"/>
+    </row>
+    <row r="128" customHeight="1" spans="1:10">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -2353,8 +2863,11 @@
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
-    </row>
-    <row r="129" customHeight="1" spans="1:7">
+      <c r="H128" s="2"/>
+      <c r="I128" s="2"/>
+      <c r="J128" s="2"/>
+    </row>
+    <row r="129" customHeight="1" spans="1:10">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -2362,8 +2875,11 @@
       <c r="E129" s="2"/>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
-    </row>
-    <row r="130" customHeight="1" spans="1:7">
+      <c r="H129" s="2"/>
+      <c r="I129" s="2"/>
+      <c r="J129" s="2"/>
+    </row>
+    <row r="130" customHeight="1" spans="1:10">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -2371,8 +2887,11 @@
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
-    </row>
-    <row r="131" customHeight="1" spans="1:7">
+      <c r="H130" s="2"/>
+      <c r="I130" s="2"/>
+      <c r="J130" s="2"/>
+    </row>
+    <row r="131" customHeight="1" spans="1:10">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -2380,8 +2899,11 @@
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
-    </row>
-    <row r="132" customHeight="1" spans="1:7">
+      <c r="H131" s="2"/>
+      <c r="I131" s="2"/>
+      <c r="J131" s="2"/>
+    </row>
+    <row r="132" customHeight="1" spans="1:10">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -2389,8 +2911,11 @@
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
-    </row>
-    <row r="133" customHeight="1" spans="1:7">
+      <c r="H132" s="2"/>
+      <c r="I132" s="2"/>
+      <c r="J132" s="2"/>
+    </row>
+    <row r="133" customHeight="1" spans="1:10">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -2398,8 +2923,11 @@
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
-    </row>
-    <row r="134" customHeight="1" spans="1:7">
+      <c r="H133" s="2"/>
+      <c r="I133" s="2"/>
+      <c r="J133" s="2"/>
+    </row>
+    <row r="134" customHeight="1" spans="1:10">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -2407,8 +2935,11 @@
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
-    </row>
-    <row r="135" customHeight="1" spans="1:7">
+      <c r="H134" s="2"/>
+      <c r="I134" s="2"/>
+      <c r="J134" s="2"/>
+    </row>
+    <row r="135" customHeight="1" spans="1:10">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -2416,8 +2947,11 @@
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
-    </row>
-    <row r="136" customHeight="1" spans="1:7">
+      <c r="H135" s="2"/>
+      <c r="I135" s="2"/>
+      <c r="J135" s="2"/>
+    </row>
+    <row r="136" customHeight="1" spans="1:10">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -2425,8 +2959,11 @@
       <c r="E136" s="2"/>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
-    </row>
-    <row r="137" customHeight="1" spans="1:7">
+      <c r="H136" s="2"/>
+      <c r="I136" s="2"/>
+      <c r="J136" s="2"/>
+    </row>
+    <row r="137" customHeight="1" spans="1:10">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -2434,8 +2971,11 @@
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
-    </row>
-    <row r="138" customHeight="1" spans="1:7">
+      <c r="H137" s="2"/>
+      <c r="I137" s="2"/>
+      <c r="J137" s="2"/>
+    </row>
+    <row r="138" customHeight="1" spans="1:10">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -2443,8 +2983,11 @@
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
-    </row>
-    <row r="139" customHeight="1" spans="1:7">
+      <c r="H138" s="2"/>
+      <c r="I138" s="2"/>
+      <c r="J138" s="2"/>
+    </row>
+    <row r="139" customHeight="1" spans="1:10">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -2452,8 +2995,11 @@
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
-    </row>
-    <row r="140" customHeight="1" spans="1:7">
+      <c r="H139" s="2"/>
+      <c r="I139" s="2"/>
+      <c r="J139" s="2"/>
+    </row>
+    <row r="140" customHeight="1" spans="1:10">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -2461,8 +3007,11 @@
       <c r="E140" s="2"/>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
-    </row>
-    <row r="141" customHeight="1" spans="1:7">
+      <c r="H140" s="2"/>
+      <c r="I140" s="2"/>
+      <c r="J140" s="2"/>
+    </row>
+    <row r="141" customHeight="1" spans="1:10">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -2470,8 +3019,11 @@
       <c r="E141" s="2"/>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
-    </row>
-    <row r="142" customHeight="1" spans="1:7">
+      <c r="H141" s="2"/>
+      <c r="I141" s="2"/>
+      <c r="J141" s="2"/>
+    </row>
+    <row r="142" customHeight="1" spans="1:10">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -2479,8 +3031,11 @@
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
-    </row>
-    <row r="143" customHeight="1" spans="1:7">
+      <c r="H142" s="2"/>
+      <c r="I142" s="2"/>
+      <c r="J142" s="2"/>
+    </row>
+    <row r="143" customHeight="1" spans="1:10">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -2488,8 +3043,11 @@
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
-    </row>
-    <row r="144" customHeight="1" spans="1:7">
+      <c r="H143" s="2"/>
+      <c r="I143" s="2"/>
+      <c r="J143" s="2"/>
+    </row>
+    <row r="144" customHeight="1" spans="1:10">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -2497,8 +3055,11 @@
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
-    </row>
-    <row r="145" customHeight="1" spans="1:7">
+      <c r="H144" s="2"/>
+      <c r="I144" s="2"/>
+      <c r="J144" s="2"/>
+    </row>
+    <row r="145" customHeight="1" spans="1:10">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -2506,8 +3067,11 @@
       <c r="E145" s="2"/>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
-    </row>
-    <row r="146" customHeight="1" spans="1:7">
+      <c r="H145" s="2"/>
+      <c r="I145" s="2"/>
+      <c r="J145" s="2"/>
+    </row>
+    <row r="146" customHeight="1" spans="1:10">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -2515,8 +3079,11 @@
       <c r="E146" s="2"/>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
-    </row>
-    <row r="147" customHeight="1" spans="1:7">
+      <c r="H146" s="2"/>
+      <c r="I146" s="2"/>
+      <c r="J146" s="2"/>
+    </row>
+    <row r="147" customHeight="1" spans="1:10">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -2524,8 +3091,11 @@
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
-    </row>
-    <row r="148" customHeight="1" spans="1:7">
+      <c r="H147" s="2"/>
+      <c r="I147" s="2"/>
+      <c r="J147" s="2"/>
+    </row>
+    <row r="148" customHeight="1" spans="1:10">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -2533,8 +3103,11 @@
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
-    </row>
-    <row r="149" customHeight="1" spans="1:7">
+      <c r="H148" s="2"/>
+      <c r="I148" s="2"/>
+      <c r="J148" s="2"/>
+    </row>
+    <row r="149" customHeight="1" spans="1:10">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -2542,8 +3115,11 @@
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
-    </row>
-    <row r="150" customHeight="1" spans="1:7">
+      <c r="H149" s="2"/>
+      <c r="I149" s="2"/>
+      <c r="J149" s="2"/>
+    </row>
+    <row r="150" customHeight="1" spans="1:10">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -2551,8 +3127,11 @@
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
-    </row>
-    <row r="151" customHeight="1" spans="1:7">
+      <c r="H150" s="2"/>
+      <c r="I150" s="2"/>
+      <c r="J150" s="2"/>
+    </row>
+    <row r="151" customHeight="1" spans="1:10">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -2560,8 +3139,11 @@
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
-    </row>
-    <row r="152" customHeight="1" spans="1:7">
+      <c r="H151" s="2"/>
+      <c r="I151" s="2"/>
+      <c r="J151" s="2"/>
+    </row>
+    <row r="152" customHeight="1" spans="1:10">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -2569,8 +3151,11 @@
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
-    </row>
-    <row r="153" customHeight="1" spans="1:7">
+      <c r="H152" s="2"/>
+      <c r="I152" s="2"/>
+      <c r="J152" s="2"/>
+    </row>
+    <row r="153" customHeight="1" spans="1:10">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -2578,8 +3163,11 @@
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
-    </row>
-    <row r="154" customHeight="1" spans="1:7">
+      <c r="H153" s="2"/>
+      <c r="I153" s="2"/>
+      <c r="J153" s="2"/>
+    </row>
+    <row r="154" customHeight="1" spans="1:10">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -2587,8 +3175,11 @@
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
-    </row>
-    <row r="155" customHeight="1" spans="1:7">
+      <c r="H154" s="2"/>
+      <c r="I154" s="2"/>
+      <c r="J154" s="2"/>
+    </row>
+    <row r="155" customHeight="1" spans="1:10">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -2596,8 +3187,11 @@
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
-    </row>
-    <row r="156" customHeight="1" spans="1:7">
+      <c r="H155" s="2"/>
+      <c r="I155" s="2"/>
+      <c r="J155" s="2"/>
+    </row>
+    <row r="156" customHeight="1" spans="1:10">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -2605,8 +3199,11 @@
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
-    </row>
-    <row r="157" customHeight="1" spans="1:7">
+      <c r="H156" s="2"/>
+      <c r="I156" s="2"/>
+      <c r="J156" s="2"/>
+    </row>
+    <row r="157" customHeight="1" spans="1:10">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -2614,8 +3211,11 @@
       <c r="E157" s="2"/>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
-    </row>
-    <row r="158" customHeight="1" spans="1:7">
+      <c r="H157" s="2"/>
+      <c r="I157" s="2"/>
+      <c r="J157" s="2"/>
+    </row>
+    <row r="158" customHeight="1" spans="1:10">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -2623,8 +3223,11 @@
       <c r="E158" s="2"/>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
-    </row>
-    <row r="159" customHeight="1" spans="1:7">
+      <c r="H158" s="2"/>
+      <c r="I158" s="2"/>
+      <c r="J158" s="2"/>
+    </row>
+    <row r="159" customHeight="1" spans="1:10">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -2632,8 +3235,11 @@
       <c r="E159" s="2"/>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
-    </row>
-    <row r="160" customHeight="1" spans="1:7">
+      <c r="H159" s="2"/>
+      <c r="I159" s="2"/>
+      <c r="J159" s="2"/>
+    </row>
+    <row r="160" customHeight="1" spans="1:10">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -2641,8 +3247,11 @@
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
-    </row>
-    <row r="161" customHeight="1" spans="1:7">
+      <c r="H160" s="2"/>
+      <c r="I160" s="2"/>
+      <c r="J160" s="2"/>
+    </row>
+    <row r="161" customHeight="1" spans="1:10">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -2650,8 +3259,11 @@
       <c r="E161" s="2"/>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
-    </row>
-    <row r="162" customHeight="1" spans="1:7">
+      <c r="H161" s="2"/>
+      <c r="I161" s="2"/>
+      <c r="J161" s="2"/>
+    </row>
+    <row r="162" customHeight="1" spans="1:10">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -2659,8 +3271,11 @@
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
-    </row>
-    <row r="163" customHeight="1" spans="1:7">
+      <c r="H162" s="2"/>
+      <c r="I162" s="2"/>
+      <c r="J162" s="2"/>
+    </row>
+    <row r="163" customHeight="1" spans="1:10">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -2668,8 +3283,11 @@
       <c r="E163" s="2"/>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
-    </row>
-    <row r="164" customHeight="1" spans="1:7">
+      <c r="H163" s="2"/>
+      <c r="I163" s="2"/>
+      <c r="J163" s="2"/>
+    </row>
+    <row r="164" customHeight="1" spans="1:10">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -2677,8 +3295,11 @@
       <c r="E164" s="2"/>
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
-    </row>
-    <row r="165" customHeight="1" spans="1:7">
+      <c r="H164" s="2"/>
+      <c r="I164" s="2"/>
+      <c r="J164" s="2"/>
+    </row>
+    <row r="165" customHeight="1" spans="1:10">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -2686,8 +3307,11 @@
       <c r="E165" s="2"/>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
-    </row>
-    <row r="166" customHeight="1" spans="1:7">
+      <c r="H165" s="2"/>
+      <c r="I165" s="2"/>
+      <c r="J165" s="2"/>
+    </row>
+    <row r="166" customHeight="1" spans="1:10">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -2695,8 +3319,11 @@
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
-    </row>
-    <row r="167" customHeight="1" spans="1:7">
+      <c r="H166" s="2"/>
+      <c r="I166" s="2"/>
+      <c r="J166" s="2"/>
+    </row>
+    <row r="167" customHeight="1" spans="1:10">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -2704,8 +3331,11 @@
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
-    </row>
-    <row r="168" customHeight="1" spans="1:7">
+      <c r="H167" s="2"/>
+      <c r="I167" s="2"/>
+      <c r="J167" s="2"/>
+    </row>
+    <row r="168" customHeight="1" spans="1:10">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -2713,8 +3343,11 @@
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
-    </row>
-    <row r="169" customHeight="1" spans="1:7">
+      <c r="H168" s="2"/>
+      <c r="I168" s="2"/>
+      <c r="J168" s="2"/>
+    </row>
+    <row r="169" customHeight="1" spans="1:10">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -2722,8 +3355,11 @@
       <c r="E169" s="2"/>
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
-    </row>
-    <row r="170" customHeight="1" spans="1:7">
+      <c r="H169" s="2"/>
+      <c r="I169" s="2"/>
+      <c r="J169" s="2"/>
+    </row>
+    <row r="170" customHeight="1" spans="1:10">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -2731,8 +3367,11 @@
       <c r="E170" s="2"/>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
-    </row>
-    <row r="171" customHeight="1" spans="1:7">
+      <c r="H170" s="2"/>
+      <c r="I170" s="2"/>
+      <c r="J170" s="2"/>
+    </row>
+    <row r="171" customHeight="1" spans="1:10">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -2740,8 +3379,11 @@
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
-    </row>
-    <row r="172" customHeight="1" spans="1:7">
+      <c r="H171" s="2"/>
+      <c r="I171" s="2"/>
+      <c r="J171" s="2"/>
+    </row>
+    <row r="172" customHeight="1" spans="1:10">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -2749,8 +3391,11 @@
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
-    </row>
-    <row r="173" customHeight="1" spans="1:7">
+      <c r="H172" s="2"/>
+      <c r="I172" s="2"/>
+      <c r="J172" s="2"/>
+    </row>
+    <row r="173" customHeight="1" spans="1:10">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -2758,8 +3403,11 @@
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
-    </row>
-    <row r="174" customHeight="1" spans="1:7">
+      <c r="H173" s="2"/>
+      <c r="I173" s="2"/>
+      <c r="J173" s="2"/>
+    </row>
+    <row r="174" customHeight="1" spans="1:10">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -2767,8 +3415,11 @@
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
-    </row>
-    <row r="175" customHeight="1" spans="1:7">
+      <c r="H174" s="2"/>
+      <c r="I174" s="2"/>
+      <c r="J174" s="2"/>
+    </row>
+    <row r="175" customHeight="1" spans="1:10">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -2776,8 +3427,11 @@
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
-    </row>
-    <row r="176" customHeight="1" spans="1:7">
+      <c r="H175" s="2"/>
+      <c r="I175" s="2"/>
+      <c r="J175" s="2"/>
+    </row>
+    <row r="176" customHeight="1" spans="1:10">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -2785,8 +3439,11 @@
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
-    </row>
-    <row r="177" customHeight="1" spans="1:7">
+      <c r="H176" s="2"/>
+      <c r="I176" s="2"/>
+      <c r="J176" s="2"/>
+    </row>
+    <row r="177" customHeight="1" spans="1:10">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -2794,8 +3451,11 @@
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
-    </row>
-    <row r="178" customHeight="1" spans="1:7">
+      <c r="H177" s="2"/>
+      <c r="I177" s="2"/>
+      <c r="J177" s="2"/>
+    </row>
+    <row r="178" customHeight="1" spans="1:10">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -2803,8 +3463,11 @@
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
-    </row>
-    <row r="179" customHeight="1" spans="1:7">
+      <c r="H178" s="2"/>
+      <c r="I178" s="2"/>
+      <c r="J178" s="2"/>
+    </row>
+    <row r="179" customHeight="1" spans="1:10">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -2812,8 +3475,11 @@
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
-    </row>
-    <row r="180" customHeight="1" spans="1:7">
+      <c r="H179" s="2"/>
+      <c r="I179" s="2"/>
+      <c r="J179" s="2"/>
+    </row>
+    <row r="180" customHeight="1" spans="1:10">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -2821,8 +3487,11 @@
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
-    </row>
-    <row r="181" customHeight="1" spans="1:7">
+      <c r="H180" s="2"/>
+      <c r="I180" s="2"/>
+      <c r="J180" s="2"/>
+    </row>
+    <row r="181" customHeight="1" spans="1:10">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -2830,8 +3499,11 @@
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
-    </row>
-    <row r="182" customHeight="1" spans="1:7">
+      <c r="H181" s="2"/>
+      <c r="I181" s="2"/>
+      <c r="J181" s="2"/>
+    </row>
+    <row r="182" customHeight="1" spans="1:10">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -2839,8 +3511,11 @@
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
-    </row>
-    <row r="183" customHeight="1" spans="1:7">
+      <c r="H182" s="2"/>
+      <c r="I182" s="2"/>
+      <c r="J182" s="2"/>
+    </row>
+    <row r="183" customHeight="1" spans="1:10">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -2848,8 +3523,11 @@
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
-    </row>
-    <row r="184" customHeight="1" spans="1:7">
+      <c r="H183" s="2"/>
+      <c r="I183" s="2"/>
+      <c r="J183" s="2"/>
+    </row>
+    <row r="184" customHeight="1" spans="1:10">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -2857,8 +3535,11 @@
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
-    </row>
-    <row r="185" customHeight="1" spans="1:7">
+      <c r="H184" s="2"/>
+      <c r="I184" s="2"/>
+      <c r="J184" s="2"/>
+    </row>
+    <row r="185" customHeight="1" spans="1:10">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -2866,8 +3547,11 @@
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
-    </row>
-    <row r="186" customHeight="1" spans="1:7">
+      <c r="H185" s="2"/>
+      <c r="I185" s="2"/>
+      <c r="J185" s="2"/>
+    </row>
+    <row r="186" customHeight="1" spans="1:10">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -2875,8 +3559,11 @@
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
-    </row>
-    <row r="187" customHeight="1" spans="1:7">
+      <c r="H186" s="2"/>
+      <c r="I186" s="2"/>
+      <c r="J186" s="2"/>
+    </row>
+    <row r="187" customHeight="1" spans="1:10">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -2884,8 +3571,11 @@
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
-    </row>
-    <row r="188" customHeight="1" spans="1:7">
+      <c r="H187" s="2"/>
+      <c r="I187" s="2"/>
+      <c r="J187" s="2"/>
+    </row>
+    <row r="188" customHeight="1" spans="1:10">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -2893,8 +3583,11 @@
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
-    </row>
-    <row r="189" customHeight="1" spans="1:7">
+      <c r="H188" s="2"/>
+      <c r="I188" s="2"/>
+      <c r="J188" s="2"/>
+    </row>
+    <row r="189" customHeight="1" spans="1:10">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -2902,8 +3595,11 @@
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
-    </row>
-    <row r="190" customHeight="1" spans="1:7">
+      <c r="H189" s="2"/>
+      <c r="I189" s="2"/>
+      <c r="J189" s="2"/>
+    </row>
+    <row r="190" customHeight="1" spans="1:10">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -2911,8 +3607,11 @@
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
-    </row>
-    <row r="191" customHeight="1" spans="1:7">
+      <c r="H190" s="2"/>
+      <c r="I190" s="2"/>
+      <c r="J190" s="2"/>
+    </row>
+    <row r="191" customHeight="1" spans="1:10">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -2920,8 +3619,11 @@
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
-    </row>
-    <row r="192" customHeight="1" spans="1:7">
+      <c r="H191" s="2"/>
+      <c r="I191" s="2"/>
+      <c r="J191" s="2"/>
+    </row>
+    <row r="192" customHeight="1" spans="1:10">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -2929,8 +3631,11 @@
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
-    </row>
-    <row r="193" customHeight="1" spans="1:7">
+      <c r="H192" s="2"/>
+      <c r="I192" s="2"/>
+      <c r="J192" s="2"/>
+    </row>
+    <row r="193" customHeight="1" spans="1:10">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -2938,8 +3643,11 @@
       <c r="E193" s="2"/>
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
-    </row>
-    <row r="194" customHeight="1" spans="1:7">
+      <c r="H193" s="2"/>
+      <c r="I193" s="2"/>
+      <c r="J193" s="2"/>
+    </row>
+    <row r="194" customHeight="1" spans="1:10">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -2947,8 +3655,11 @@
       <c r="E194" s="2"/>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
-    </row>
-    <row r="195" customHeight="1" spans="1:7">
+      <c r="H194" s="2"/>
+      <c r="I194" s="2"/>
+      <c r="J194" s="2"/>
+    </row>
+    <row r="195" customHeight="1" spans="1:10">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -2956,8 +3667,11 @@
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
-    </row>
-    <row r="196" customHeight="1" spans="1:7">
+      <c r="H195" s="2"/>
+      <c r="I195" s="2"/>
+      <c r="J195" s="2"/>
+    </row>
+    <row r="196" customHeight="1" spans="1:10">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -2965,8 +3679,11 @@
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
-    </row>
-    <row r="197" customHeight="1" spans="1:7">
+      <c r="H196" s="2"/>
+      <c r="I196" s="2"/>
+      <c r="J196" s="2"/>
+    </row>
+    <row r="197" customHeight="1" spans="1:10">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -2974,8 +3691,11 @@
       <c r="E197" s="2"/>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
-    </row>
-    <row r="198" customHeight="1" spans="1:7">
+      <c r="H197" s="2"/>
+      <c r="I197" s="2"/>
+      <c r="J197" s="2"/>
+    </row>
+    <row r="198" customHeight="1" spans="1:10">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -2983,8 +3703,11 @@
       <c r="E198" s="2"/>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
-    </row>
-    <row r="199" customHeight="1" spans="1:7">
+      <c r="H198" s="2"/>
+      <c r="I198" s="2"/>
+      <c r="J198" s="2"/>
+    </row>
+    <row r="199" customHeight="1" spans="1:10">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -2992,8 +3715,11 @@
       <c r="E199" s="2"/>
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
-    </row>
-    <row r="200" customHeight="1" spans="1:7">
+      <c r="H199" s="2"/>
+      <c r="I199" s="2"/>
+      <c r="J199" s="2"/>
+    </row>
+    <row r="200" customHeight="1" spans="1:10">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -3001,13 +3727,25 @@
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
+      <c r="H200" s="2"/>
+      <c r="I200" s="2"/>
+      <c r="J200" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" sqref="A18:A200">
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="A2:A200">
       <formula1>"建筑施工,危险化学品,通用"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F2:F200">
+    <dataValidation type="list" errorTitle="无效输入" error="适用地区至少选择到省级；全国适用请选择全国。" promptTitle="适用地区" prompt="请选择全国或省级地区" sqref="B2:B200">
+      <formula1>省</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C2:C200">
+      <formula1>IF($B2="","",INDIRECT("P_"&amp;$B2))</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D2:D200">
+      <formula1>IF($C2="","",INDIRECT("C_"&amp;$C2))</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="I2:I200">
       <formula1>"国家标准,行业标准,地方标准,企业标准"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3019,7 +3757,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" customHeight="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3028,130 +3766,304 @@
     <col min="4" max="4" width="56" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:4">
+    <row r="1" ht="37" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" ht="29" customHeight="1" spans="1:4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" ht="37" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" ht="29" customHeight="1" spans="1:4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" ht="37" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" ht="29" customHeight="1" spans="1:4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" ht="37" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" ht="29" customHeight="1" spans="1:4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" ht="37" customHeight="1" spans="1:4">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" ht="29" customHeight="1" spans="1:4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" ht="37" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" ht="29" customHeight="1" spans="1:4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" ht="37" customHeight="1" spans="1:4">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" ht="29" customHeight="1" spans="1:4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" ht="37" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" ht="37" customHeight="1" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" ht="37" customHeight="1" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" ht="37" customHeight="1" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" ht="29" customHeight="1" spans="1:4">
-      <c r="A9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>33</v>
+      <c r="C11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" ht="37" customHeight="1" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:Q8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <sheetData>
+    <row r="1" spans="1:17">
+      <c r="A1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" t="s">
+        <v>56</v>
+      </c>
+      <c r="J7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" t="s">
+        <v>66</v>
+      </c>
+      <c r="K8" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" t="s">
+        <v>68</v>
+      </c>
+      <c r="M8" t="s">
+        <v>69</v>
+      </c>
+      <c r="N8" t="s">
+        <v>70</v>
+      </c>
+      <c r="O8" t="s">
+        <v>12</v>
+      </c>
+      <c r="P8" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
